--- a/school_data.xlsx
+++ b/school_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marwa\source\repos\Grading\Grading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66CEB812-936D-4E40-801C-63BB6F00B064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB1B9237-0E49-4B65-8180-59557F218F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{E94A38D3-6609-4CF0-A501-16BA2825DC25}"/>
+    <workbookView xWindow="2664" yWindow="2664" windowWidth="17280" windowHeight="9960" xr2:uid="{E94A38D3-6609-4CF0-A501-16BA2825DC25}"/>
   </bookViews>
   <sheets>
     <sheet name="Students_List" sheetId="2" r:id="rId1"/>
@@ -450,7 +450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204EF9B8-5043-4B1C-827C-831F7078D7E4}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
@@ -474,6 +474,14 @@
       </c>
       <c r="F1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -506,6 +514,10 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <f>Students_List!A2</f>
+        <v>1</v>
+      </c>
       <c r="K2" t="s">
         <v>9</v>
       </c>

--- a/school_data.xlsx
+++ b/school_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marwa\source\repos\Grading\Grading\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB1B9237-0E49-4B65-8180-59557F218F4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{973C8ADB-00C5-4146-A01D-5447FAD1DAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2664" yWindow="2664" windowWidth="17280" windowHeight="9960" xr2:uid="{E94A38D3-6609-4CF0-A501-16BA2825DC25}"/>
+    <workbookView xWindow="2664" yWindow="2664" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{E94A38D3-6609-4CF0-A501-16BA2825DC25}"/>
   </bookViews>
   <sheets>
     <sheet name="Students_List" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>National_ID</t>
   </si>
@@ -79,6 +79,18 @@
   </si>
   <si>
     <t>rejected</t>
+  </si>
+  <si>
+    <t>بيبس</t>
+  </si>
+  <si>
+    <t>بيسب</t>
+  </si>
+  <si>
+    <t>يبسيب</t>
+  </si>
+  <si>
+    <t>يبيب</t>
   </si>
 </sst>
 </file>
@@ -483,6 +495,18 @@
       <c r="B2">
         <v>1</v>
       </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
